--- a/teaching/advanced-econometrics/labs/12-polynomial-centering/polynomial_centering.xlsx
+++ b/teaching/advanced-econometrics/labs/12-polynomial-centering/polynomial_centering.xlsx
@@ -3738,10 +3738,10 @@
         <x:v>x</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>Exposure or predictor X</x:v>
+        <x:v>Regressor entering the polynomial (raw, not centered)</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
-        <x:v>centered units</x:v>
+        <x:v>X units</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
         <x:v>No missing values.</x:v>
